--- a/sheets/조재수대금교본/검수/봄처녀.xlsx
+++ b/sheets/조재수대금교본/검수/봄처녀.xlsx
@@ -4407,7 +4407,6 @@
       <c r="P9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
-ﾉ
 太</t>
         </is>
       </c>
@@ -4422,7 +4421,6 @@
       <c r="T9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
-ﾉ
 太</t>
         </is>
       </c>

--- a/sheets/조재수대금교본/검수/봄처녀.xlsx
+++ b/sheets/조재수대금교본/검수/봄처녀.xlsx
@@ -4407,6 +4407,7 @@
       <c r="P9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
+ﾉ
 太</t>
         </is>
       </c>
@@ -4421,6 +4422,7 @@
       <c r="T9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
+ﾉ
 太</t>
         </is>
       </c>

--- a/sheets/조재수대금교본/검수/봄처녀.xlsx
+++ b/sheets/조재수대금교본/검수/봄처녀.xlsx
@@ -3953,32 +3953,32 @@
   </sheetPr>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="10.71" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="10.71" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="10.71" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="10.71" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="10.71" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="10.71" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="9" customWidth="1"/>
+    <col min="14" max="14" width="10.71" customWidth="1"/>
     <col min="15" max="15" width="6" customWidth="1"/>
-    <col min="16" max="16" width="9" customWidth="1"/>
+    <col min="16" max="16" width="10.71" customWidth="1"/>
     <col min="17" max="17" width="6" customWidth="1"/>
-    <col min="18" max="18" width="9" customWidth="1"/>
+    <col min="18" max="18" width="10.71" customWidth="1"/>
     <col min="19" max="19" width="6" customWidth="1"/>
-    <col min="20" max="20" width="9" customWidth="1"/>
+    <col min="20" max="20" width="10.71" customWidth="1"/>
     <col min="21" max="21" width="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="71.43" customHeight="true">
+    <row r="2" ht="80.0" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -4005,7 +4005,7 @@
       <c r="T2" s="20"/>
       <c r="U2" s="20"/>
     </row>
-    <row r="3" ht="106.4" customHeight="true">
+    <row r="3" ht="119.22" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -4068,7 +4068,7 @@
       </c>
       <c r="U3" s="22"/>
     </row>
-    <row r="4" ht="106.4" customHeight="true">
+    <row r="4" ht="119.22" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -4131,7 +4131,7 @@
       </c>
       <c r="U4" s="23"/>
     </row>
-    <row r="5" ht="106.4" customHeight="true">
+    <row r="5" ht="119.22" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21"/>
       <c r="C5" s="24"/>
@@ -4154,7 +4154,7 @@
       <c r="T5" s="21"/>
       <c r="U5" s="24"/>
     </row>
-    <row r="6" ht="106.4" customHeight="true">
+    <row r="6" ht="119.22" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -4217,7 +4217,7 @@
       </c>
       <c r="U6" s="22"/>
     </row>
-    <row r="7" ht="106.4" customHeight="true">
+    <row r="7" ht="119.22" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -4280,7 +4280,7 @@
       </c>
       <c r="U7" s="23"/>
     </row>
-    <row r="8" ht="106.4" customHeight="true">
+    <row r="8" ht="119.22" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -4353,7 +4353,7 @@
       </c>
       <c r="U8" s="24"/>
     </row>
-    <row r="9" ht="106.4" customHeight="true">
+    <row r="9" ht="119.22" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -4428,7 +4428,7 @@
       </c>
       <c r="U9" s="22"/>
     </row>
-    <row r="10" ht="106.4" customHeight="true">
+    <row r="10" ht="119.22" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
@@ -4491,7 +4491,7 @@
       </c>
       <c r="U10" s="23"/>
     </row>
-    <row r="11" ht="106.4" customHeight="true">
+    <row r="11" ht="119.22" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21"/>
       <c r="C11" s="24"/>
@@ -4514,7 +4514,7 @@
       <c r="T11" s="21"/>
       <c r="U11" s="24"/>
     </row>
-    <row r="12" ht="106.4" customHeight="true">
+    <row r="12" ht="119.22" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="21"/>
       <c r="C12" s="22"/>
@@ -4537,7 +4537,7 @@
       <c r="T12" s="21"/>
       <c r="U12" s="22"/>
     </row>
-    <row r="13" ht="106.4" customHeight="true">
+    <row r="13" ht="119.22" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21"/>
       <c r="C13" s="23"/>
@@ -4560,7 +4560,7 @@
       <c r="T13" s="21"/>
       <c r="U13" s="23"/>
     </row>
-    <row r="14" ht="106.4" customHeight="true">
+    <row r="14" ht="119.22" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>
@@ -4626,7 +4626,7 @@
     <row r="15" ht="6.0" customHeight="true">
       <c r="A15" s="0"/>
     </row>
-    <row r="16" ht="71.43" customHeight="true">
+    <row r="16" ht="80.0" customHeight="true">
       <c r="A16" s="0"/>
       <c r="B16" s="20" t="inlineStr">
         <is>
@@ -4653,7 +4653,7 @@
       <c r="T16" s="20"/>
       <c r="U16" s="20"/>
     </row>
-    <row r="17" ht="106.4" customHeight="true">
+    <row r="17" ht="119.22" customHeight="true">
       <c r="A17" s="0"/>
       <c r="B17" s="21"/>
       <c r="C17" s="22"/>
@@ -4684,7 +4684,7 @@
       </c>
       <c r="U17" s="22"/>
     </row>
-    <row r="18" ht="106.4" customHeight="true">
+    <row r="18" ht="119.22" customHeight="true">
       <c r="A18" s="0"/>
       <c r="B18" s="21"/>
       <c r="C18" s="23"/>
@@ -4715,7 +4715,7 @@
       </c>
       <c r="U18" s="23"/>
     </row>
-    <row r="19" ht="106.4" customHeight="true">
+    <row r="19" ht="119.22" customHeight="true">
       <c r="A19" s="0"/>
       <c r="B19" s="21"/>
       <c r="C19" s="24"/>
@@ -4738,7 +4738,7 @@
       <c r="T19" s="21"/>
       <c r="U19" s="24"/>
     </row>
-    <row r="20" ht="106.4" customHeight="true">
+    <row r="20" ht="119.22" customHeight="true">
       <c r="A20" s="0"/>
       <c r="B20" s="21"/>
       <c r="C20" s="22"/>
@@ -4769,7 +4769,7 @@
       </c>
       <c r="U20" s="22"/>
     </row>
-    <row r="21" ht="106.4" customHeight="true">
+    <row r="21" ht="119.22" customHeight="true">
       <c r="A21" s="0"/>
       <c r="B21" s="21"/>
       <c r="C21" s="23"/>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="U21" s="23"/>
     </row>
-    <row r="22" ht="106.4" customHeight="true">
+    <row r="22" ht="119.22" customHeight="true">
       <c r="A22" s="0"/>
       <c r="B22" s="21"/>
       <c r="C22" s="24"/>
@@ -4833,7 +4833,7 @@
       </c>
       <c r="U22" s="24"/>
     </row>
-    <row r="23" ht="106.4" customHeight="true">
+    <row r="23" ht="119.22" customHeight="true">
       <c r="A23" s="0"/>
       <c r="B23" s="21"/>
       <c r="C23" s="22"/>
@@ -4866,7 +4866,7 @@
       </c>
       <c r="U23" s="22"/>
     </row>
-    <row r="24" ht="106.4" customHeight="true">
+    <row r="24" ht="119.22" customHeight="true">
       <c r="A24" s="0"/>
       <c r="B24" s="21"/>
       <c r="C24" s="23"/>
@@ -4897,7 +4897,7 @@
       </c>
       <c r="U24" s="23"/>
     </row>
-    <row r="25" ht="106.4" customHeight="true">
+    <row r="25" ht="119.22" customHeight="true">
       <c r="A25" s="0"/>
       <c r="B25" s="21"/>
       <c r="C25" s="24"/>
@@ -4920,7 +4920,7 @@
       <c r="T25" s="21"/>
       <c r="U25" s="24"/>
     </row>
-    <row r="26" ht="106.4" customHeight="true">
+    <row r="26" ht="119.22" customHeight="true">
       <c r="A26" s="0"/>
       <c r="B26" s="21"/>
       <c r="C26" s="22"/>
@@ -4943,7 +4943,7 @@
       <c r="T26" s="21"/>
       <c r="U26" s="22"/>
     </row>
-    <row r="27" ht="106.4" customHeight="true">
+    <row r="27" ht="119.22" customHeight="true">
       <c r="A27" s="0"/>
       <c r="B27" s="21"/>
       <c r="C27" s="23"/>
@@ -4966,7 +4966,7 @@
       <c r="T27" s="21"/>
       <c r="U27" s="23"/>
     </row>
-    <row r="28" ht="106.4" customHeight="true">
+    <row r="28" ht="119.22" customHeight="true">
       <c r="A28" s="0"/>
       <c r="B28" s="21"/>
       <c r="C28" s="24"/>
@@ -5004,7 +5004,7 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="56"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="50"/>
   <rowBreaks count="1" manualBreakCount="1">
     <brk id="14" max="16383" man="1"/>
   </rowBreaks>
